--- a/Testing_Data/2026_06_Festo/PressureSensorCalibration_updated.xlsx
+++ b/Testing_Data/2026_06_Festo/PressureSensorCalibration_updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE6083A-E3D0-4CBA-8978-7EA0FCF7AB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937CD3E5-0030-4EFA-8F1F-7C180A0E7975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ED23B71C-6DC7-4F03-A302-FE33CB0246DD}"/>
+    <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{ED23B71C-6DC7-4F03-A302-FE33CB0246DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={46343613-9834-4FD4-9F19-3AD9135CE7DD}</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{46343613-9834-4FD4-9F19-3AD9135CE7DD}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Inferred, not measured</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
   <si>
     <t>Voltage (V)</t>
   </si>
@@ -52,12 +70,24 @@
   <si>
     <t>Sample</t>
   </si>
+  <si>
+    <t>Serial</t>
+  </si>
+  <si>
+    <t>Predicted</t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>serial</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -72,6 +102,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -129,6 +165,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>P(voltage)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -203,9 +264,17 @@
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.26952559055118108"/>
+                  <c:y val="1.0081815782528371E-2"/>
+                </c:manualLayout>
+              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
-                <a:noFill/>
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
                 <a:ln>
                   <a:noFill/>
                 </a:ln>
@@ -218,10 +287,7 @@
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
+                        <a:schemeClr val="bg1"/>
                       </a:solidFill>
                       <a:latin typeface="+mn-lt"/>
                       <a:ea typeface="+mn-ea"/>
@@ -235,60 +301,99 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$12</c:f>
+              <c:f>Sheet1!$B$2:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>0.1603</c:v>
+                  <c:v>0.19550342130987292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6033999999999999</c:v>
+                  <c:v>4.6480938416422291</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.9638</c:v>
+                  <c:v>1.3538611925708699</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.6070000000000002</c:v>
+                  <c:v>1.4711632453567938</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.2726999999999999</c:v>
+                  <c:v>1.9696969696969697</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.9348000000000001</c:v>
+                  <c:v>2.6246334310850439</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.6547000000000001</c:v>
+                  <c:v>3.2942326490713589</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.6999022482893449</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.9687194525904204</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.139784946236559</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$12</c:f>
+              <c:f>Sheet1!$C$2:$C$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>250</c:v>
+                  <c:v>700</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>400</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
+                  <c:v>560</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>600</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>700</c:v>
+                <c:pt idx="9">
+                  <c:v>620</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -502,6 +607,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>P(serial)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -576,9 +706,17 @@
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.32537160979877516"/>
+                  <c:y val="9.9869281045751636E-3"/>
+                </c:manualLayout>
+              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
-                <a:noFill/>
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
                 <a:ln>
                   <a:noFill/>
                 </a:ln>
@@ -591,10 +729,7 @@
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
+                        <a:schemeClr val="bg1"/>
                       </a:solidFill>
                       <a:latin typeface="+mn-lt"/>
                       <a:ea typeface="+mn-ea"/>
@@ -608,29 +743,77 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$M$2:$M$3</c:f>
+              <c:f>Sheet1!$A$2:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0.83579999999999999</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.7897999999999996</c:v>
+                  <c:v>951</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>277</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>301</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>403</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>537</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>674</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>757</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>812</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>847</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$N$2:$N$3</c:f>
+              <c:f>Sheet1!$C$2:$C$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>560</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>620</c:v>
                 </c:pt>
               </c:numCache>
@@ -639,7 +822,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2BD6-41CE-8E74-4D384B49972E}"/>
+              <c16:uniqueId val="{00000001-9960-491D-B1EE-BEE672B66A7C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1946,16 +2129,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>177165</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>93345</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>481965</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>150495</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1982,16 +2165,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>6667</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>80962</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>236220</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>82867</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2017,6 +2200,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Ben Bolen" id="{54D18D7C-9DDF-439C-BA6E-9E4E4285BAD9}" userId="S::bbolen@pdx.edu::2756ab96-c1b4-4d6e-be6a-ace1ad4a8569" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2314,156 +2503,272 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B1" dT="2026-07-18T06:15:09.88" personId="{54D18D7C-9DDF-439C-BA6E-9E4E4285BAD9}" id="{46343613-9834-4FD4-9F19-3AD9135CE7DD}">
+    <text>Inferred, not measured</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F07EB23B-8D5C-452B-917B-439C5A6B7860}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F07EB23B-8D5C-452B-917B-439C5A6B7860}">
   <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>40</v>
+      </c>
+      <c r="B2">
+        <f>A2*5/1023</f>
+        <v>0.19550342130987292</v>
+      </c>
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>1</v>
-      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>0.1603</v>
-      </c>
-      <c r="B2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>951</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B18" si="0">A3*5/1023</f>
+        <v>4.6480938416422291</v>
+      </c>
+      <c r="C3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>277</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>1.3538611925708699</v>
+      </c>
+      <c r="C4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>301</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>1.4711632453567938</v>
+      </c>
+      <c r="C5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>403</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>1.9696969696969697</v>
+      </c>
+      <c r="C6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>537</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>2.6246334310850439</v>
+      </c>
+      <c r="C7">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>674</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>3.2942326490713589</v>
+      </c>
+      <c r="C8">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>757</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>3.6999022482893449</v>
+      </c>
+      <c r="C9">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>812</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>3.9687194525904204</v>
+      </c>
+      <c r="C10">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>847</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>4.139784946236559</v>
+      </c>
+      <c r="C11">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>0.83579999999999999</v>
-      </c>
-      <c r="N2">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1.6033999999999999</v>
-      </c>
-      <c r="B3">
-        <v>250</v>
-      </c>
-      <c r="M3">
-        <v>4.7897999999999996</v>
-      </c>
-      <c r="N3">
-        <v>620</v>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1.9638</v>
-      </c>
-      <c r="B4">
-        <v>300</v>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2.6070000000000002</v>
-      </c>
-      <c r="B5">
-        <v>400</v>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>3.2726999999999999</v>
-      </c>
-      <c r="B6">
-        <v>500</v>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>3.9348000000000001</v>
-      </c>
-      <c r="B7">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>4.6547000000000001</v>
-      </c>
-      <c r="B8">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
-        <v>4</v>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" t="s">
+      <c r="C22" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B23">
-        <v>0.1676</v>
-      </c>
-      <c r="C23">
-        <f>154.97*B23-10.004</f>
-        <v>15.968971999999999</v>
-      </c>
-      <c r="N23" t="s">
+      <c r="C23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O23" t="s">
+      <c r="N23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B24">
-        <v>4.0956000000000001</v>
-      </c>
       <c r="C24">
-        <f>154.97*B24-10.004</f>
-        <v>624.69113200000004</v>
+        <v>839</v>
+      </c>
+      <c r="D24">
+        <f>C24*0.7572-13.995</f>
+        <v>621.29579999999999</v>
+      </c>
+      <c r="E24">
+        <v>620</v>
+      </c>
+      <c r="M24">
+        <v>0.19</v>
       </c>
       <c r="N24">
-        <v>0.83579999999999999</v>
-      </c>
-      <c r="O24">
-        <f>156.8*N24-131.06</f>
-        <v>-6.5600000000074488E-3</v>
+        <f>M24*154.92-13.955</f>
+        <v>15.479799999999999</v>
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D25">
+        <f t="shared" ref="D25:D28" si="1">C25*0.7572-13.995</f>
+        <v>-13.994999999999999</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
       <c r="N25">
-        <v>4.7214</v>
-      </c>
-      <c r="O25">
-        <f>156.8*N25-131.06</f>
-        <v>609.25552000000016</v>
+        <f t="shared" ref="N25:N27" si="2">M25*155.61-14.908</f>
+        <v>296.31200000000001</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>